--- a/eciCW773/data/BayesianGrowthRates.xlsx
+++ b/eciCW773/data/BayesianGrowthRates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\ECOMAP\ECOMAP\eciCW773\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B8A12B-208F-4437-9A39-F9C0EA67EDD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1AF1A69-D6D0-4EB0-BE71-5F39F5AD3862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6405" yWindow="2565" windowWidth="28800" windowHeight="14805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="150" yWindow="1545" windowWidth="28995" windowHeight="17685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="20">
   <si>
     <t>aerobic</t>
   </si>
@@ -101,10 +101,6 @@
   </si>
   <si>
     <t>EX_glyc_e</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EX_xyl__D_e</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -452,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -575,7 +571,7 @@
         <v>0.53</v>
       </c>
       <c r="J3">
-        <v>0.56999999999999995</v>
+        <v>-0.56999999999999995</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>16</v>
@@ -617,7 +613,7 @@
         <v>2.92</v>
       </c>
       <c r="J4">
-        <v>3.29</v>
+        <v>-3.29</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>16</v>
@@ -659,7 +655,7 @@
         <v>5.48</v>
       </c>
       <c r="J5">
-        <v>5.5</v>
+        <v>-5.5</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>16</v>
@@ -701,7 +697,7 @@
         <v>6.13</v>
       </c>
       <c r="J6">
-        <v>6.61</v>
+        <v>-6.61</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>16</v>
@@ -1051,45 +1047,9 @@
       <c r="N14" s="2"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15">
-        <v>-3.35</v>
-      </c>
-      <c r="D15">
-        <v>0.11</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>1</v>
-      </c>
+      <c r="I15"/>
+      <c r="K15"/>
+      <c r="L15"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="I16"/>
@@ -1162,9 +1122,16 @@
       <c r="L29"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="I30"/>
-      <c r="K30"/>
-      <c r="L30"/>
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="M30" s="1"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
@@ -1374,7 +1341,6 @@
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -1385,7 +1351,6 @@
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -1396,6 +1361,7 @@
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -1458,17 +1424,6 @@
       <c r="J55" s="1"/>
       <c r="M55" s="1"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="M56" s="1"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
